--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-immunization.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-immunization.xlsx
@@ -370,7 +370,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -608,7 +608,7 @@
     <t>ワクチンが投与されなかった理由。 / The reason why a vaccine was not administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -787,7 +787,7 @@
     <t>主要なソースからのものではないレコードのデータのソース。 / The source of the data for a record which is not from a primary source.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-origin</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-origin|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=INF].role[classCode=PAT] (this syntax for self-reported) .participation[typeCode=INF].role[classCode=LIC] (this syntax for health care professional) .participation[typeCode=INF].role[classCode=PRS] (this syntax for family member)</t>
@@ -911,7 +911,7 @@
     <t>ワクチンが投与されたルート。 / The route by which the vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-route|4.0.1</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1024,7 +1024,7 @@
     <t>予防接種イベントで開業医または組織が果たす役割。 / The role a practitioner or organization plays in the immunization event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-function</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1092,7 +1092,7 @@
     <t>ワクチンが投与された理由。 / The reason why a vaccine was administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1104,7 +1104,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1147,7 +1147,7 @@
     <t>用量がサブポテントと見なされる理由。 / The reason why a dose is considered to be subpotent.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-subpotent-reason|4.0.1</t>
   </si>
   <si>
     <t>Immunization.education</t>
@@ -1229,7 +1229,7 @@
     <t>患者の予防接種プログラムの適格性。 / The patient's eligibility for a vaccation program.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-program-eligibility|4.0.1</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 64994-7</t>
@@ -1247,7 +1247,7 @@
     <t>投与されたワクチンの購入に使用される資金源。 / The source of funding used to purchase the vaccine administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-funding-source|4.0.1</t>
   </si>
   <si>
     <t>Immunization.reaction</t>
@@ -1292,7 +1292,7 @@
     <t>Immunization.reaction.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1353,7 +1353,7 @@
     <t>Immunization.protocolApplied.authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1375,7 +1375,7 @@
     <t>ワクチン予防可能な疾患用量が投与されています。 / The vaccine preventable disease the dose is being administered for.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-target-disease|4.0.1</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]</t>
